--- a/output/normativa_ia_mexico_20260531_1702_cleaned.xlsx
+++ b/output/normativa_ia_mexico_20260531_1702_cleaned.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30125"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_87DBDD32D47A00CFEB3B98154B5DCE3AE7CF2EDC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF838963-6B8E-490A-A10C-CE4B23AD99D5}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_87DBDD32D47A00CFEB3B98154B5DCE3AE7CF2EDC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{302C9903-1493-41C7-A939-8FA5D74F893F}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -991,16 +991,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:N43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="62.85546875" customWidth="1"/>
+    <col min="4" max="4" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="40.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1041,7 +1042,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1081,8 +1082,12 @@
       <c r="M2" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="N2" t="str">
+        <f>IF(COUNTIF($D$2:$D$10, D2)&gt;0, "Valid", "Invalid")</f>
+        <v>Valid</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1123,7 +1128,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -1164,7 +1169,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1205,7 +1210,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1246,7 +1251,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -1287,7 +1292,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -1328,7 +1333,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -1369,7 +1374,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -1410,7 +1415,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1451,7 +1456,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -1492,7 +1497,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -1533,7 +1538,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -1574,7 +1579,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -1615,7 +1620,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
         <v>13</v>
       </c>
